--- a/ThoDenNgay_Project_Manager.xlsx
+++ b/ThoDenNgay_Project_Manager.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\alo-tho-master\alo-tho-master\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0E5FF2A-ACD9-4715-A3E3-52B42842CAE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{548EBE4B-A3E3-4350-AFE7-C13FB107E43F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{FB6F2678-4D5D-41EF-A2F7-B07D6FFAA270}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="43">
   <si>
     <t>Sprint</t>
   </si>
@@ -124,6 +124,42 @@
   </si>
   <si>
     <t>Tách trang, dữ liệu và luồng tạo khách thu cước</t>
+  </si>
+  <si>
+    <t>Location</t>
+  </si>
+  <si>
+    <t>Tự động lưu GPS sau đăng nhập</t>
+  </si>
+  <si>
+    <t>Khách và thợ; từ chối quyền không chặn đăng nhập</t>
+  </si>
+  <si>
+    <t>feat(location): auto save user location on login</t>
+  </si>
+  <si>
+    <t>GPS login 100m hoặc 5 phút</t>
+  </si>
+  <si>
+    <t>Tự động cập nhật vị trí khi đăng nhập</t>
+  </si>
+  <si>
+    <t>Thông báo GPS nhỏ khi cập nhật thành công</t>
+  </si>
+  <si>
+    <t>profiles</t>
+  </si>
+  <si>
+    <t>Thêm latitude, longitude, last_location_at, location_updated_by</t>
+  </si>
+  <si>
+    <t>migration_login_location.sql</t>
+  </si>
+  <si>
+    <t>GPS đăng nhập là best-effort</t>
+  </si>
+  <si>
+    <t>Từ chối hoặc lỗi GPS không được chặn đăng nhập</t>
   </si>
 </sst>
 </file>
@@ -491,14 +527,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78466453-D086-41EC-9B2F-D6741F75C8DD}">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="49" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="46.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -532,6 +568,23 @@
         <v>46212</v>
       </c>
     </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" s="2">
+        <v>46212</v>
+      </c>
+      <c r="E3" t="s">
+        <v>33</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
@@ -540,11 +593,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5927262C-D85D-42F1-AF93-990A6B26A44C}">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="48.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8.7109375" bestFit="1" customWidth="1"/>
@@ -593,6 +646,26 @@
       </c>
       <c r="G2" t="s">
         <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" s="2">
+        <v>46212</v>
+      </c>
+      <c r="G3" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -640,15 +713,15 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{069D4428-9083-4750-B53B-7D9773A67264}">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="41.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="48.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="40" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -688,6 +761,26 @@
         <v>28</v>
       </c>
     </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3" t="s">
+        <v>37</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -695,7 +788,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A785C6D0-79B6-4091-8C7B-BDD1457F842E}">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
@@ -703,7 +796,7 @@
     <col min="3" max="3" width="36.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="86.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="38.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="43.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -741,6 +834,26 @@
       </c>
       <c r="E2" t="s">
         <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2">
+        <v>46212</v>
+      </c>
+      <c r="C3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F3" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -784,14 +897,14 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F9190C6-E9DF-4BE3-8EC0-220A0F680284}">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="78.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="47.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="43.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -825,6 +938,23 @@
         <v>26</v>
       </c>
     </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2">
+        <v>46212</v>
+      </c>
+      <c r="C3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E3" t="s">
+        <v>34</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/ThoDenNgay_Project_Manager.xlsx
+++ b/ThoDenNgay_Project_Manager.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\alo-tho-master\alo-tho-master\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{548EBE4B-A3E3-4350-AFE7-C13FB107E43F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5E491D9-A430-4B3A-B021-962C6882088C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{FB6F2678-4D5D-41EF-A2F7-B07D6FFAA270}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="55">
   <si>
     <t>Sprint</t>
   </si>
@@ -160,6 +160,42 @@
   </si>
   <si>
     <t>Từ chối hoặc lỗi GPS không được chặn đăng nhập</t>
+  </si>
+  <si>
+    <t>Multi-service</t>
+  </si>
+  <si>
+    <t>Bộ chọn dịch vụ phân cấp cho khách, thợ và admin</t>
+  </si>
+  <si>
+    <t>Tái sử dụng job_services và fallback service_id</t>
+  </si>
+  <si>
+    <t>feat: support multi-service job with hierarchical service selector</t>
+  </si>
+  <si>
+    <t>Một commit; tree checkbox dùng chung</t>
+  </si>
+  <si>
+    <t>Multi-service job với hierarchical selector</t>
+  </si>
+  <si>
+    <t>Khách, thợ tạo nhanh, admin tạo job</t>
+  </si>
+  <si>
+    <t>jobs / job_services</t>
+  </si>
+  <si>
+    <t>Job mới lưu quan hệ nhiều-nhiều; jobs.service_id giữ làm primary và fallback legacy</t>
+  </si>
+  <si>
+    <t>migration_smart_service_workflow.sql</t>
+  </si>
+  <si>
+    <t>Không tạo migration trùng job_services</t>
+  </si>
+  <si>
+    <t>Migration workflow hiện có đã tạo bảng, index và backfill; chỉ tái sử dụng</t>
   </si>
 </sst>
 </file>
@@ -527,10 +563,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78466453-D086-41EC-9B2F-D6741F75C8DD}">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="49" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.7109375" bestFit="1" customWidth="1"/>
@@ -585,6 +621,23 @@
         <v>33</v>
       </c>
     </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="2">
+        <v>46212</v>
+      </c>
+      <c r="E4" t="s">
+        <v>45</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
@@ -593,12 +646,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5927262C-D85D-42F1-AF93-990A6B26A44C}">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="48.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="59" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8.42578125" bestFit="1" customWidth="1"/>
@@ -666,6 +719,26 @@
       </c>
       <c r="G3" t="s">
         <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" s="2">
+        <v>46212</v>
+      </c>
+      <c r="G4" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -713,14 +786,14 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{069D4428-9083-4750-B53B-7D9773A67264}">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="41.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="48.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="59" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="40" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -779,6 +852,26 @@
       </c>
       <c r="F3" t="s">
         <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" t="s">
+        <v>46</v>
+      </c>
+      <c r="F4" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -788,7 +881,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A785C6D0-79B6-4091-8C7B-BDD1457F842E}">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
@@ -796,7 +889,7 @@
     <col min="3" max="3" width="36.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="86.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="38.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="43.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="59" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -854,6 +947,26 @@
       </c>
       <c r="F3" t="s">
         <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2">
+        <v>46212</v>
+      </c>
+      <c r="C4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F4" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -897,14 +1010,14 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F9190C6-E9DF-4BE3-8EC0-220A0F680284}">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="78.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="47.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="43.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="66.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="59" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -955,6 +1068,23 @@
         <v>34</v>
       </c>
     </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2">
+        <v>46212</v>
+      </c>
+      <c r="C4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E4" t="s">
+        <v>46</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/ThoDenNgay_Project_Manager.xlsx
+++ b/ThoDenNgay_Project_Manager.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\alo-tho-master\alo-tho-master\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5E491D9-A430-4B3A-B021-962C6882088C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FA1BE23-B265-4B44-B370-88B513DF03C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{FB6F2678-4D5D-41EF-A2F7-B07D6FFAA270}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="70">
   <si>
     <t>Sprint</t>
   </si>
@@ -196,6 +196,51 @@
   </si>
   <si>
     <t>Migration workflow hiện có đã tạo bảng, index và backfill; chỉ tái sử dụng</t>
+  </si>
+  <si>
+    <t>Sprint nền tảng mở rộng</t>
+  </si>
+  <si>
+    <t>Feature Registry và Dynamic Menu cho trang Thợ</t>
+  </si>
+  <si>
+    <t>Done</t>
+  </si>
+  <si>
+    <t>Menu thợ sinh từ registry; BillGo chỉ hiện khi tài khoản có dữ liệu BillGo.</t>
+  </si>
+  <si>
+    <t>feat(worker): add feature registry and dynamic module menu system</t>
+  </si>
+  <si>
+    <t>Pending commit</t>
+  </si>
+  <si>
+    <t>pending</t>
+  </si>
+  <si>
+    <t>Cập nhật sau khi tạo commit.</t>
+  </si>
+  <si>
+    <t>Feature Registry và Dynamic Menu trang Thợ</t>
+  </si>
+  <si>
+    <t>Nền tảng module theo quyền/ngành nghề/dữ liệu thực tế.</t>
+  </si>
+  <si>
+    <t>Worker Feature Registry</t>
+  </si>
+  <si>
+    <t>Không đổi schema; điều kiện BillGo đọc từ billgo_subscriptions/billgo_receivables.</t>
+  </si>
+  <si>
+    <t>Không có</t>
+  </si>
+  <si>
+    <t>Menu thợ chuyển sang Feature Registry</t>
+  </si>
+  <si>
+    <t>Chuẩn bị mở rộng module theo ngành nghề, quyền hạn và dữ liệu sử dụng.</t>
   </si>
 </sst>
 </file>
@@ -562,9 +607,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78466453-D086-41EC-9B2F-D6741F75C8DD}">
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{78466453-D086-41EC-9B2F-D6741F75C8DD}">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultRowHeight="15" ns3:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="49" bestFit="1" customWidth="1"/>
@@ -573,7 +618,7 @@
     <col min="5" max="5" width="46.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" s="1" customFormat="1" ns3:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -590,7 +635,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ns3:dyDescent="0.25">
       <c r="A2" t="s">
         <v>19</v>
       </c>
@@ -604,7 +649,7 @@
         <v>46212</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ns3:dyDescent="0.25">
       <c r="A3" t="s">
         <v>31</v>
       </c>
@@ -621,7 +666,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" ns3:dyDescent="0.25">
       <c r="A4" t="s">
         <v>43</v>
       </c>
@@ -636,6 +681,31 @@
       </c>
       <c r="E4" t="s">
         <v>45</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ns3:dyDescent="0.25">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Sprint nen tang mo rong</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Feature Registry va Dynamic Menu cho trang Tho</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Hoan thanh</t>
+        </is>
+      </c>
+      <c r="D5" s="2">
+        <v>46212</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Menu tho sinh tu registry; BillGo chi hien khi tai khoan co du lieu BillGo.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -645,9 +715,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5927262C-D85D-42F1-AF93-990A6B26A44C}">
-  <dimension ref="A1:G4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{5927262C-D85D-42F1-AF93-990A6B26A44C}">
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr defaultRowHeight="15" ns3:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
@@ -658,7 +728,7 @@
     <col min="7" max="7" width="43.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" s="1" customFormat="1" ns3:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
@@ -681,7 +751,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ns3:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -701,7 +771,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ns3:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -721,7 +791,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ns3:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -739,6 +809,39 @@
       </c>
       <c r="G4" t="s">
         <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ns3:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Sprint nen tang mo rong</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>feat(worker): add feature registry and dynamic module menu system</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>San sang commit</t>
+        </is>
+      </c>
+      <c r="E5" s="2">
+        <v>46212</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Cap nhat hash sau khi tao commit.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -785,9 +888,9 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{069D4428-9083-4750-B53B-7D9773A67264}">
-  <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{069D4428-9083-4750-B53B-7D9773A67264}">
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr defaultRowHeight="15" ns3:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="41.7109375" bestFit="1" customWidth="1"/>
@@ -797,7 +900,7 @@
     <col min="6" max="6" width="40" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" s="1" customFormat="1" ns3:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
@@ -817,7 +920,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ns3:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -834,7 +937,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ns3:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -854,7 +957,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ns3:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -872,6 +975,36 @@
       </c>
       <c r="F4" t="s">
         <v>49</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ns3:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Feature Registry va Dynamic Menu trang Tho</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Sprint nen tang mo rong</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Hoan thanh</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>feat(worker): add feature registry and dynamic module menu system</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Nen tang module theo quyen/nganh nghe/du lieu thuc te.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -880,9 +1013,9 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A785C6D0-79B6-4091-8C7B-BDD1457F842E}">
-  <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{A785C6D0-79B6-4091-8C7B-BDD1457F842E}">
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr defaultRowHeight="15" ns3:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.7109375" bestFit="1" customWidth="1"/>
@@ -892,7 +1025,7 @@
     <col min="6" max="6" width="59" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" s="1" customFormat="1" ns3:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
@@ -912,7 +1045,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ns3:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -929,7 +1062,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ns3:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -949,7 +1082,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ns3:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -967,6 +1100,34 @@
       </c>
       <c r="F4" t="s">
         <v>46</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ns3:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2">
+        <v>46212</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Worker Feature Registry</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Khong doi schema; dieu kien BillGo doc tu billgo_subscriptions/billgo_receivables.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Khong co</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>feat(worker): add feature registry and dynamic module menu system</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1009,9 +1170,9 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F9190C6-E9DF-4BE3-8EC0-220A0F680284}">
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{0F9190C6-E9DF-4BE3-8EC0-220A0F680284}">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultRowHeight="15" ns3:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.7109375" bestFit="1" customWidth="1"/>
@@ -1020,7 +1181,7 @@
     <col min="5" max="6" width="59" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" s="1" customFormat="1" ns3:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
@@ -1037,7 +1198,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ns3:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1051,7 +1212,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ns3:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1068,7 +1229,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" ns3:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1083,6 +1244,29 @@
       </c>
       <c r="E4" t="s">
         <v>46</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ns3:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2">
+        <v>46212</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Menu tho chuyen sang Feature Registry</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Chuan bi mo rong module theo nganh nghe, quyen han va du lieu su dung.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>feat(worker): add feature registry and dynamic module menu system</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/ThoDenNgay_Project_Manager.xlsx
+++ b/ThoDenNgay_Project_Manager.xlsx
@@ -608,7 +608,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{78466453-D086-41EC-9B2F-D6741F75C8DD}">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="15" ns3:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.7109375" bestFit="1" customWidth="1"/>
@@ -708,6 +708,31 @@
         </is>
       </c>
     </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>BillGo</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Chuan hoa dung truoc - thu sau va han thanh toan ngay 20</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Hoan thanh</t>
+        </is>
+      </c>
+      <c r="D6" s="2">
+        <v>46212</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Moi ky co period_start, period_end, due_date va status tinh theo han.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
@@ -716,7 +741,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{5927262C-D85D-42F1-AF93-990A6B26A44C}">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15" ns3:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
@@ -839,6 +864,39 @@
         </is>
       </c>
       <c r="G5" t="inlineStr">
+        <is>
+          <t>Cap nhat hash sau khi tao commit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>BillGo</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>feat(billgo): implement postpaid billing cycle with due date management</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>San sang commit</t>
+        </is>
+      </c>
+      <c r="E6" s="2">
+        <v>46212</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>Cap nhat hash sau khi tao commit.</t>
         </is>
@@ -889,7 +947,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{069D4428-9083-4750-B53B-7D9773A67264}">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15" ns3:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
@@ -1007,6 +1065,36 @@
         </is>
       </c>
     </row>
+    <row r="6" spans="1:6">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>BillGo postpaid billing cycle</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>BillGo</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Hoan thanh</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>feat(billgo): implement postpaid billing cycle with due date management</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ho tro chu ky 1/3/6/12 thang va due date ngay 20 thang sau.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1014,7 +1102,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{A785C6D0-79B6-4091-8C7B-BDD1457F842E}">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15" ns3:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
@@ -1127,6 +1215,34 @@
       <c r="F5" t="inlineStr">
         <is>
           <t>feat(worker): add feature registry and dynamic module menu system</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2">
+        <v>46212</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>billgo_receivables</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Them status not_due/due; backfill period_start, period_end, due_date theo postpaid.</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>migration_billgo_postpaid_cycles.sql</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>feat(billgo): implement postpaid billing cycle with due date management</t>
         </is>
       </c>
     </row>
@@ -1171,7 +1287,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{0F9190C6-E9DF-4BE3-8EC0-220A0F680284}">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="15" ns3:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
@@ -1269,6 +1385,29 @@
         </is>
       </c>
     </row>
+    <row r="6" spans="1:5">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2">
+        <v>46212</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>BillGo dung truoc - thu sau</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Han thanh toan la ngay 20 cua thang ke tiep sau ky su dung.</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>feat(billgo): implement postpaid billing cycle with due date management</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/ThoDenNgay_Project_Manager.xlsx
+++ b/ThoDenNgay_Project_Manager.xlsx
@@ -608,7 +608,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{78466453-D086-41EC-9B2F-D6741F75C8DD}">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="15" ns3:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.7109375" bestFit="1" customWidth="1"/>
@@ -733,6 +733,31 @@
         </is>
       </c>
     </row>
+    <row r="7" spans="1:5">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Worker access control</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Loc module va dich vu theo nganh nghe tho da duyet</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Hoan thanh</t>
+        </is>
+      </c>
+      <c r="D7" s="2">
+        <v>46213</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Fallback an toan chi hien Cong viec, Khach hang, Ho so khi chua co nganh.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
@@ -741,7 +766,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{5927262C-D85D-42F1-AF93-990A6B26A44C}">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15" ns3:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
@@ -902,15 +927,48 @@
         </is>
       </c>
     </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Worker access control</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>fix(worker): filter worker modules and services by approved categories</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>San sang commit</t>
+        </is>
+      </c>
+      <c r="E7" s="2">
+        <v>46213</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Cap nhat hash sau khi tao commit.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43849B92-9A8E-48A5-A516-516C5F2B5AF9}">
-  <dimension ref="A1:F1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{43849B92-9A8E-48A5-A516-516C5F2B5AF9}">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="15" ns3:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="4.28515625" bestFit="1" customWidth="1"/>
@@ -920,7 +978,7 @@
     <col min="6" max="6" width="6.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" s="1" customFormat="1" ns3:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
@@ -938,6 +996,34 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Trang tho hien tat ca nganh nghe/dich vu khong dung specialties</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>Da sua</t>
+        </is>
+      </c>
+      <c r="D2" s="1">
+        <v>46213</v>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>fix(worker): filter worker modules and services by approved categories</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>Doi sang strict specialty filtering cho menu va quick job services.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -947,7 +1033,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{069D4428-9083-4750-B53B-7D9773A67264}">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15" ns3:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
@@ -1092,6 +1178,36 @@
       <c r="F6" t="inlineStr">
         <is>
           <t>Ho tro chu ky 1/3/6/12 thang va due date ngay 20 thang sau.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Filter worker modules/services by approved categories</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Worker access control</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Hoan thanh</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>fix(worker): filter worker modules and services by approved categories</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ap dung cho menu worker va tao viec nhanh.</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1403,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{0F9190C6-E9DF-4BE3-8EC0-220A0F680284}">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="15" ns3:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
@@ -1408,6 +1524,29 @@
         </is>
       </c>
     </row>
+    <row r="7" spans="1:5">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2">
+        <v>46213</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Worker specialties la dieu kien hien thi module/dich vu</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Tho khong co nganh ro rang khong thay module nganh chuyen biet.</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>fix(worker): filter worker modules and services by approved categories</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/ThoDenNgay_Project_Manager.xlsx
+++ b/ThoDenNgay_Project_Manager.xlsx
@@ -766,7 +766,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{5927262C-D85D-42F1-AF93-990A6B26A44C}">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15" ns3:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
@@ -960,6 +960,80 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Worker specialization filter</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>fix(worker): prevent cross-category service matches</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Committed</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr" s="2">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>current commit</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Fix PC worker page showing unrelated service categories caused by generic child-service name matching.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Worker specialization filter</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>fix(worker): prevent cross-category service matches</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Committed</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr" s="2">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>current commit</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Fix PC worker page showing unrelated service categories caused by generic child-service name matching.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -967,7 +1041,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{43849B92-9A8E-48A5-A516-516C5F2B5AF9}">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15" ns3:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
@@ -1026,6 +1100,80 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr" s="1">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr" s="1">
+        <is>
+          <t>Worker page shows unrelated services for workers registered to limited categories</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr" s="1">
+        <is>
+          <t>Fixed in pending commit</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr" s="1">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr" s="1">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr" s="1">
+        <is>
+          <t>fix(worker): prevent cross-category service matches</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Service matching no longer allows broad child labels such as Lap dat/Sua chua to match across industries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr" s="1">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr" s="1">
+        <is>
+          <t>Worker page shows unrelated services for workers registered to limited categories</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr" s="1">
+        <is>
+          <t>Fixed in pending commit</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr" s="1">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr" s="1">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr" s="1">
+        <is>
+          <t>fix(worker): prevent cross-category service matches</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Service matching no longer allows broad child labels such as Lap dat/Sua chua to match across industries.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1033,7 +1181,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{069D4428-9083-4750-B53B-7D9773A67264}">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15" ns3:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
@@ -1208,6 +1356,80 @@
       <c r="F7" t="inlineStr">
         <is>
           <t>Ap dung cho menu worker va tao viec nhanh.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Worker category-scoped service display</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Worker specialization filter</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>fix(worker): prevent cross-category service matches</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Quick job/service lists now respect approved worker categories more strictly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Worker category-scoped service display</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Worker specialization filter</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>fix(worker): prevent cross-category service matches</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Quick job/service lists now respect approved worker categories more strictly.</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1625,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{0F9190C6-E9DF-4BE3-8EC0-220A0F680284}">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="15" ns3:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
@@ -1547,6 +1769,50 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr" s="2">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Worker service filtering must be category-aware; generic child service labels cannot be used as cross-industry matches.</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>fix(worker): prevent cross-category service matches</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr" s="2">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Worker service filtering must be category-aware; generic child service labels cannot be used as cross-industry matches.</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>fix(worker): prevent cross-category service matches</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/ThoDenNgay_Project_Manager.xlsx
+++ b/ThoDenNgay_Project_Manager.xlsx
@@ -608,7 +608,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{78466453-D086-41EC-9B2F-D6741F75C8DD}">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="15" ns3:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.7109375" bestFit="1" customWidth="1"/>
@@ -758,6 +758,60 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Worker sales inventory</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Remove BillGo from worker inventory product setup and sales order creation</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Hoan thanh</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Kho hang/ban hang cua tho chi phuc vu ban hang; BillGo giu o module rieng.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Worker sales inventory</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Remove BillGo from worker inventory product setup and sales order creation</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Hoan thanh</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Kho hang/ban hang cua tho chi phuc vu ban hang; BillGo giu o module rieng.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
@@ -766,7 +820,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{5927262C-D85D-42F1-AF93-990A6B26A44C}">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15" ns3:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
@@ -1034,6 +1088,80 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Worker sales inventory</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>fix(worker-sales): keep BillGo out of inventory sales</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Ready to commit</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Removed BillGo controls from worker inventory/sales; sales RPC always disables BillGo creation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Worker sales inventory</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>fix(worker-sales): keep BillGo out of inventory sales</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Ready to commit</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Removed BillGo controls from worker inventory/sales; sales RPC always disables BillGo creation.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1041,7 +1169,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{43849B92-9A8E-48A5-A516-516C5F2B5AF9}">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15" ns3:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
@@ -1174,6 +1302,70 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Worker inventory/sales exposes BillGo flow for normal worker product sales</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Fixed in pending commit</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>fix(worker-sales): keep BillGo out of inventory sales</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Removed recurring BillGo product flag UI and disabled BillGo creation from sales orders.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Worker inventory/sales exposes BillGo flow for normal worker product sales</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Fixed in pending commit</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>fix(worker-sales): keep BillGo out of inventory sales</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Removed recurring BillGo product flag UI and disabled BillGo creation from sales orders.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1181,7 +1373,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{069D4428-9083-4750-B53B-7D9773A67264}">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15" ns3:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
@@ -1430,6 +1622,70 @@
       <c r="G9" t="inlineStr">
         <is>
           <t>Quick job/service lists now respect approved worker categories more strictly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Keep BillGo out of worker inventory sales flow</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Worker sales inventory</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>fix(worker-sales): keep BillGo out of inventory sales</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Inventory products and sales orders are worker-only sales data; BillGo remains a separate module.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Keep BillGo out of worker inventory sales flow</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Worker sales inventory</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>fix(worker-sales): keep BillGo out of inventory sales</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Inventory products and sales orders are worker-only sales data; BillGo remains a separate module.</t>
         </is>
       </c>
     </row>

--- a/ThoDenNgay_Project_Manager.xlsx
+++ b/ThoDenNgay_Project_Manager.xlsx
@@ -608,7 +608,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{78466453-D086-41EC-9B2F-D6741F75C8DD}">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="15" ns3:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.7109375" bestFit="1" customWidth="1"/>
@@ -812,6 +812,38 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Worker Sales/Inventory</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Tự động tạo mã sản phẩm theo danh mục khi thợ thêm sản phẩm; giữ mã khi sửa sản phẩm.</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>feat: tự động tạo mã sản phẩm theo danh mục</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
@@ -820,7 +852,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{5927262C-D85D-42F1-AF93-990A6B26A44C}">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr defaultRowHeight="15" ns3:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
@@ -1162,6 +1194,28 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>feat: tự động tạo mã sản phẩm theo danh mục</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Worker inventory product code auto-generation by category prefix, per worker scope, duplicate handling, migration for missing codes.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1169,7 +1223,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{43849B92-9A8E-48A5-A516-516C5F2B5AF9}">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="15" ns3:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
@@ -1366,6 +1420,33 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Worker inventory product code collision</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Không lấy tổng số sản phẩm + 1; lấy số lớn nhất theo tiền tố trong từng worker rồi cộng 1, retry khi insert trùng.</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>feat: tự động tạo mã sản phẩm theo danh mục</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1373,7 +1454,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{069D4428-9083-4750-B53B-7D9773A67264}">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="15" ns3:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
@@ -1686,6 +1767,33 @@
       <c r="F11" t="inlineStr">
         <is>
           <t>Inventory products and sales orders are worker-only sales data; BillGo remains a separate module.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Auto product code by category</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NET/CAM/PC/PRI/SP prefix, readonly auto field, custom code override, search by SKU already supported.</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>feat: tự động tạo mã sản phẩm theo danh mục</t>
         </is>
       </c>
     </row>

--- a/ThoDenNgay_Project_Manager.xlsx
+++ b/ThoDenNgay_Project_Manager.xlsx
@@ -608,7 +608,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{78466453-D086-41EC-9B2F-D6741F75C8DD}">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15" ns3:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.7109375" bestFit="1" customWidth="1"/>
@@ -844,6 +844,38 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Worker Dashboard</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Thêm thống kê hôm nay cho bảng điều khiển thợ: khách hàng, đánh giá, tổng tiền.</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>feat(worker-dashboard): add today stats</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
@@ -852,7 +884,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{5927262C-D85D-42F1-AF93-990A6B26A44C}">
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="15" ns3:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
@@ -1216,6 +1248,28 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>feat(worker-dashboard): add today stats</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Add compact today customer, rating, and collected amount stats below worker dashboard summary.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1223,7 +1277,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{43849B92-9A8E-48A5-A516-516C5F2B5AF9}">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="15" ns3:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
@@ -1447,6 +1501,33 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Worker dashboard lacks daily operational stats</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Bổ sung hàng thống kê hôm nay và format tiền gọn.</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>feat(worker-dashboard): add today stats</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1454,7 +1535,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{069D4428-9083-4750-B53B-7D9773A67264}">
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr defaultRowHeight="15" ns3:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
@@ -1794,6 +1875,33 @@
       <c r="E12" t="inlineStr">
         <is>
           <t>feat: tự động tạo mã sản phẩm theo danh mục</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Worker dashboard today stats</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Hiển thị khách hôm nay, đánh giá hôm nay, tổng tiền hôm nay.</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>feat(worker-dashboard): add today stats</t>
         </is>
       </c>
     </row>

--- a/ThoDenNgay_Project_Manager.xlsx
+++ b/ThoDenNgay_Project_Manager.xlsx
@@ -608,7 +608,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{78466453-D086-41EC-9B2F-D6741F75C8DD}">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="15" ns3:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.7109375" bestFit="1" customWidth="1"/>
@@ -876,6 +876,38 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Worker Dashboard</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Gộp thống kê hôm nay vào card tổng quan, hiển thị Tháng 7/Hôm nay 12/07 và thêm nút nổi Tạo việc trên mobile.</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>feat(worker-dashboard): optimize mobile stats layout</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
@@ -884,7 +916,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{5927262C-D85D-42F1-AF93-990A6B26A44C}">
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr defaultRowHeight="15" ns3:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
@@ -1270,6 +1302,28 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>feat(worker-dashboard): optimize mobile stats layout</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Optimize worker dashboard stats layout for mobile and add floating quick job action.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1277,7 +1331,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{43849B92-9A8E-48A5-A516-516C5F2B5AF9}">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="15" ns3:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
@@ -1528,6 +1582,33 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Quick job action pushed too low on mobile</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Gộp hàng Hôm nay vào cùng card thống kê, thêm nút nổi Tạo việc.</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>feat(worker-dashboard): optimize mobile stats layout</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1535,7 +1616,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{069D4428-9083-4750-B53B-7D9773A67264}">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="15" ns3:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
@@ -1902,6 +1983,33 @@
       <c r="E13" t="inlineStr">
         <is>
           <t>feat(worker-dashboard): add today stats</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Worker dashboard mobile quick action</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Nút nổi Tạo việc mở form tạo việc nhanh và cuộn tới đúng khu vực.</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>feat(worker-dashboard): optimize mobile stats layout</t>
         </is>
       </c>
     </row>

--- a/ThoDenNgay_Project_Manager.xlsx
+++ b/ThoDenNgay_Project_Manager.xlsx
@@ -608,7 +608,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{78466453-D086-41EC-9B2F-D6741F75C8DD}">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="15" ns3:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.7109375" bestFit="1" customWidth="1"/>
@@ -908,6 +908,38 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Worker backlog jobs</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>??i n?t mobile C?ng vi?c th?nh T?n vi?c, li?n k?t t?i danh s?ch vi?c c? ch?a l?m v? gi? n?t + m? t?o vi?c nhanh.</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>feat(worker): show old backlog jobs</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
@@ -916,7 +948,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{5927262C-D85D-42F1-AF93-990A6B26A44C}">
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr defaultRowHeight="15" ns3:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
@@ -1324,6 +1356,28 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>feat(worker): show old backlog jobs</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Mobile worker nav uses T?n vi?c for unfinished jobs from previous months and + opens quick job form.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1331,7 +1385,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{43849B92-9A8E-48A5-A516-516C5F2B5AF9}">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultRowHeight="15" ns3:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
@@ -1609,6 +1663,33 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Mobile C?ng vi?c label and link did not match old unfinished job workflow</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>??i nh?n th?nh T?n vi?c, l?c b? vi?c th?ng hi?n t?i v? s?a n?t + v? t?o vi?c nhanh.</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>feat(worker): show old backlog jobs</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1616,7 +1697,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{069D4428-9083-4750-B53B-7D9773A67264}">
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="15" ns3:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
@@ -2010,6 +2091,38 @@
       <c r="E14" t="inlineStr">
         <is>
           <t>feat(worker-dashboard): optimize mobile stats layout</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Worker old backlog jobs list</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Worker mobile</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>feat(worker): show old backlog jobs</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Hi?n th? vi?c ch?a ho?n th?nh t? c?c th?ng tr??c; kh?ng hi?n th? vi?c trong th?ng hi?n t?i.</t>
         </is>
       </c>
     </row>

--- a/ThoDenNgay_Project_Manager.xlsx
+++ b/ThoDenNgay_Project_Manager.xlsx
@@ -608,7 +608,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{78466453-D086-41EC-9B2F-D6741F75C8DD}">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr defaultRowHeight="15" ns3:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.7109375" bestFit="1" customWidth="1"/>
@@ -940,6 +940,38 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Worker inventory category suggestions</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Filter product category suggestions in worker inventory by worker specialties, with compact fallback suggestions.</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>feat(worker-inventory): filter category suggestions by specialty</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
@@ -948,7 +980,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{5927262C-D85D-42F1-AF93-990A6B26A44C}">
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr defaultRowHeight="15" ns3:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
@@ -1378,6 +1410,28 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>feat(worker-inventory): filter category suggestions by specialty</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Inventory add/edit product form shows compact category suggestions based on worker specialties.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1385,7 +1439,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{43849B92-9A8E-48A5-A516-516C5F2B5AF9}">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15" ns3:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
@@ -1690,6 +1744,33 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Inventory category suggestions either too limited or too broad for each worker specialty</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Suggestions now use worker specialties and keep common fallback categories only.</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>feat(worker-inventory): filter category suggestions by specialty</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1697,7 +1778,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{069D4428-9083-4750-B53B-7D9773A67264}">
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr defaultRowHeight="15" ns3:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
@@ -2123,6 +2204,38 @@
       <c r="F15" t="inlineStr">
         <is>
           <t>Hi?n th? vi?c ch?a ho?n th?nh t? c?c th?ng tr??c; kh?ng hi?n th? vi?c trong th?ng hi?n t?i.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Specialty-based inventory category suggestions</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Worker Inventory</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>feat(worker-inventory): filter category suggestions by specialty</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Add/edit product category datalist is tailored to internet, camera, computer, printer, low-voltage, or other specialties.</t>
         </is>
       </c>
     </row>

--- a/ThoDenNgay_Project_Manager.xlsx
+++ b/ThoDenNgay_Project_Manager.xlsx
@@ -608,7 +608,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{78466453-D086-41EC-9B2F-D6741F75C8DD}">
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="15" ns3:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.7109375" bestFit="1" customWidth="1"/>
@@ -972,6 +972,38 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Worker dashboard today label</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Shorten today stats label to show day number only on worker dashboard.</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>chore(worker-dashboard): shorten today stat label</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
@@ -980,7 +1012,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{5927262C-D85D-42F1-AF93-990A6B26A44C}">
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr defaultRowHeight="15" ns3:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
@@ -1432,6 +1464,28 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>chore(worker-dashboard): shorten today stat label</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Worker dashboard today stats label now uses day-only format.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1439,7 +1493,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{43849B92-9A8E-48A5-A516-516C5F2B5AF9}">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="15" ns3:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
@@ -1771,6 +1825,33 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Today stats label includes month and takes extra mobile space</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Show only day number in today stat label.</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>chore(worker-dashboard): shorten today stat label</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1778,7 +1859,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{069D4428-9083-4750-B53B-7D9773A67264}">
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="15" ns3:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
@@ -2236,6 +2317,38 @@
       <c r="F16" t="inlineStr">
         <is>
           <t>Add/edit product category datalist is tailored to internet, camera, computer, printer, low-voltage, or other specialties.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Worker dashboard compact today label</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Worker Dashboard</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>chore(worker-dashboard): shorten today stat label</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Today stat labels use day-only display for cleaner mobile cards.</t>
         </is>
       </c>
     </row>

--- a/ThoDenNgay_Project_Manager.xlsx
+++ b/ThoDenNgay_Project_Manager.xlsx
@@ -608,7 +608,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{78466453-D086-41EC-9B2F-D6741F75C8DD}">
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr defaultRowHeight="15" ns3:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.7109375" bestFit="1" customWidth="1"/>
@@ -1004,6 +1004,38 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Worker availability toggle</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Add Online/Offline toggle so active workers can pause receiving new jobs.</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>feat(worker): add availability toggle</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
@@ -1012,7 +1044,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{5927262C-D85D-42F1-AF93-990A6B26A44C}">
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr defaultRowHeight="15" ns3:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
@@ -1486,6 +1518,28 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>feat(worker): add availability toggle</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Worker dashboard availability toggle, admin assignment filtering, and database migration.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1493,7 +1547,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{43849B92-9A8E-48A5-A516-516C5F2B5AF9}">
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr defaultRowHeight="15" ns3:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
@@ -1852,6 +1906,33 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Workers cannot pause new job intake without blocking account</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Add separate is_available flag and hide/block new job intake while Offline.</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>feat(worker): add availability toggle</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1859,7 +1940,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{069D4428-9083-4750-B53B-7D9773A67264}">
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr defaultRowHeight="15" ns3:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
@@ -2349,6 +2430,38 @@
       <c r="F17" t="inlineStr">
         <is>
           <t>Today stat labels use day-only display for cleaner mobile cards.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Worker Online/Offline availability</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Worker Dashboard</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>feat(worker): add availability toggle</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Th? active c? th? chuy?n Offline ?? ngh?, kh?ng nh?n vi?c m?i nh?ng v?n gi? t?i kho?n ho?t ??ng.</t>
         </is>
       </c>
     </row>

--- a/ThoDenNgay_Project_Manager.xlsx
+++ b/ThoDenNgay_Project_Manager.xlsx
@@ -608,7 +608,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{78466453-D086-41EC-9B2F-D6741F75C8DD}">
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="15" ns3:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.7109375" bestFit="1" customWidth="1"/>
@@ -1036,6 +1036,38 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Worker inventory category rename</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Allow workers to rename existing inventory categories to fix typos without changing the category model.</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>feat(worker-inventory): allow category rename</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
@@ -1044,7 +1076,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{5927262C-D85D-42F1-AF93-990A6B26A44C}">
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr defaultRowHeight="15" ns3:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
@@ -1540,6 +1572,28 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>feat(worker-inventory): allow category rename</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Inline category rename updates all products in that category for the current worker.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1547,7 +1601,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{43849B92-9A8E-48A5-A516-516C5F2B5AF9}">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="15" ns3:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
@@ -1933,6 +1987,33 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Inventory category typo requires editing products one by one</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Add category rename action on worker inventory list.</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>feat(worker-inventory): allow category rename</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1940,7 +2021,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{069D4428-9083-4750-B53B-7D9773A67264}">
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr defaultRowHeight="15" ns3:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
@@ -2462,6 +2543,38 @@
       <c r="F18" t="inlineStr">
         <is>
           <t>Th? active c? th? chuy?n Offline ?? ngh?, kh?ng nh?n vi?c m?i nh?ng v?n gi? t?i kho?n ho?t ??ng.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Rename worker inventory category</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Worker Inventory</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>feat(worker-inventory): allow category rename</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Keep existing free-text category model, only add rename for typo correction.</t>
         </is>
       </c>
     </row>
